--- a/webapp/public/templates/12. MẠNG NGOẠI VI_BẢO.xlsx
+++ b/webapp/public/templates/12. MẠNG NGOẠI VI_BẢO.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B8_BAO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B9_BAO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,58 +414,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Cột 1</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>Tổ Hạ Tầng</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cột 5</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cột 6</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Cột 7</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cột 8</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Cột 9</t>
+          <t>Cáp Quang</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cột 10</t>
+          <t>Cáp Quang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>TTVT</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PON &gt;50 T4</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Tăng</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Giảm (T7-T6)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Tái diễn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
         </is>
       </c>
     </row>

--- a/webapp/public/templates/12. MẠNG NGOẠI VI_BẢO.xlsx
+++ b/webapp/public/templates/12. MẠNG NGOẠI VI_BẢO.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,14 +472,520 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tổ Hạ Tầng</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>96FO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>48FO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>36FO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24FO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>16FO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>12FO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8FO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6FO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tổ Hạ Tầng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>96FO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>48FO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>36FO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24FO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16FO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>12FO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8FO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6FO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16042</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4802</t>
         </is>
       </c>
     </row>
@@ -494,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,14 +1058,1188 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Bến Lức</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Cần Đước</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Cần Giuộc</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Đức Hòa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Đức Huệ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Bến Cầu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Trảng Bàng</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Gò Dầu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Kiến Tường - Mộc Hóa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Thạnh Hóa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Thạnh</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Vĩnh Hưng - Tân Hưng</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Long An</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Trụ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tầm Vu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tân An</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Thủ Thừa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Châu</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Biên</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Dương Minh Châu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Tân Ninh</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Hòa Thành</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Trung tâm Viễn thông Châu Thành</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tây Ninh</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
